--- a/neuroblastoma/results/RNA-seq/RNA-seq_shRNA_pairwise/TGFP_DOX_vs_CTRL_fgsea_results.xlsx
+++ b/neuroblastoma/results/RNA-seq/RNA-seq_shRNA_pairwise/TGFP_DOX_vs_CTRL_fgsea_results.xlsx
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.0381628909049257</v>
+        <v>0.0391956336118146</v>
       </c>
       <c r="E2">
         <v>-0.176984171617828</v>
       </c>
       <c r="F2">
-        <v>-0.472323032492076</v>
+        <v>-0.474318495590844</v>
       </c>
       <c r="G2">
         <v>55</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.522167487684729</v>
+        <v>0.465558194774347</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0.0880945010398517</v>
+        <v>0.0925528864684773</v>
       </c>
       <c r="E3">
         <v>0.341265662978493</v>
       </c>
       <c r="F3">
-        <v>0.961930619184051</v>
+        <v>0.983507635203294</v>
       </c>
       <c r="G3">
         <v>56</v>
@@ -532,13 +532,13 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.0598603117764473</v>
+        <v>0.0609039347452418</v>
       </c>
       <c r="E4">
         <v>0.142062339449957</v>
       </c>
       <c r="F4">
-        <v>0.494976735181098</v>
+        <v>0.48681674995296</v>
       </c>
       <c r="G4">
         <v>194</v>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.997797356828194</v>
+        <v>0.997777777777778</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0.0501934252649434</v>
+        <v>0.0506004243853618</v>
       </c>
       <c r="E5">
         <v>0.160662405578152</v>
       </c>
       <c r="F5">
-        <v>0.381107822383738</v>
+        <v>0.378848234245895</v>
       </c>
       <c r="G5">
         <v>21</v>
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.980349344978166</v>
+        <v>0.984615384615385</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0.0506004243853618</v>
+        <v>0.0507027937029348</v>
       </c>
       <c r="E6">
         <v>0.212131776189646</v>
       </c>
       <c r="F6">
-        <v>0.496334026708695</v>
+        <v>0.500449198784422</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -667,20 +667,20 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.0232248320654428</v>
+        <v>0.0236501012290726</v>
       </c>
       <c r="E7">
-        <v>-0.110648283857588</v>
+        <v>-0.130375510840717</v>
       </c>
       <c r="F7">
-        <v>-0.39800152834318</v>
+        <v>-0.467870619264811</v>
       </c>
       <c r="G7">
-        <v>839</v>
+        <v>858</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AP000944.5; DNAH5; AL928654.4; APLN; AC112777.1; NPR3; C1QTNF2; PET117; GFRA1; PTTG1; KCNJ12; CCDC85C; KRTAP2-3; NIPAL1; KCNB1; BDKRB1; HIVEP1; NCAPG; SLC7A6; C8orf58; SULT1B1; PCLAF; CARD10; MFSD2A; BCYRN1; SLC2A1; TTC4; CENPM; MIR137HG; ORC1; CIP2A; MIS18A; PHF19; ASF1B; KAZN; KRT18; ARHGAP23; C19orf48; ADAMTS15; CD3EAP; TENT5B; HAUS2; RBM14; CDCA5; MAP3K7CL; WDR4; AL049840.6; RFX2; GPRC5A; EIF4A1P10; PSRC1; PKN3; MYBBP1A; TLX3; CDC20; JMJD6; PAWR; IMPDH1; TNFRSF19; TMEM155; PTPN14; SLCO2A1; VSIR; CRIM1-DT; SEPTIN11; DZIP1L; NLRP1; SKA1; TEAD4; DOCK10; SHCBP1; PKP4; PADI2; RAD18; CDC45; PDGFA; MTCL1; RRM1; RFC2; AL590004.3; C1orf112; BYSL; RAD51; PIMREG; POLQ; NAT1; POLR3K; VKORC1L1; AC125807.2; SVIP; DHX37; CTIF; KRT81; RCC1; FASTKD2; CDCA3; ELN; RAB8A; PLK1; SLC16A3; MT1E; GSG1; MAGOH; BOLA2B; SAMD4A; SH2D5; SYDE1; UBASH3B; ARL13B; UPP1; KRT8; MAFK; RRP15; SNRPB; PLEKHA7; MIR503HG; NEK7; CTHRC1; U2SURP; AC055839.2; SCARB1; RPS6KA6; GLIPR2; AK6; FLNC; URB2; DOP1B; NOL6; TK1; PIEZO1; HMCES; RANGAP1; BCAR1; PRPS1; SRGAP2C; TUBB6; TUBAP2; UTP4; H2AX; TEDC1; NOP14; PTPRF; UHRF1; ERCC2; KIF20A; ALYREF; SRSF2; ABCE1; RNASEH2A; LRP8; MKI67; RACGAP1; DNTTIP2; SLC7A5; BCAR3; EXOSC3; CCN1; NSUN2; PHLDA2; TFAM; TFDP1; NUAK2; JPT2; ZNF469; STK32B; DBNDD2; TBC1D31; ADORA2B; PUS1; NAA15; CCNB2; MAK16; AMOTL2; SEC14L1; UBE2S; MAMLD1; RAB11FIP1; FSTL3; HASPIN; WDR62; KIF4A; GTPBP4; GRWD1; DUSP5; CITED2; RCL1; RRP1B; OTUD6B; FRMD6; FAM207A; EPAS1; C20orf27; WDR66; TXNRD2; CTNNAL1</t>
+          <t>AP000944.5; TMC3; DNAH5; AL928654.4; BEST3; AC007040.2; APLN; AC112777.1; NPR3; PSG6; OIP5; C1QTNF2; MTF1; PET117; GFRA1; PTTG1; KCNJ12; CCDC85C; KRTAP2-3; NIPAL1; KCNB1; BDKRB1; HIVEP1; NCAPG; SLC7A6; C8orf58; SULT1B1; PCLAF; PSG2; AC090409.1; TNNC1; MFSD2A; BCYRN1; SLC2A1; TTC4; MIR137HG; ORC1; LINC02535; CIP2A; AC108941.2; GCNT4; KCTD4; PHF19; ASF1B; KAZN; KRT18; ARHGAP23; C19orf48; ADAMTS15; CD3EAP; PADI1; TENT5B; HAUS2; RBM14; CDCA5; MAP3K7CL; WDR4; GPRC5A; FAM234B; PSRC1; RIMKLB; PKN3; MYBBP1A; TLX3; CDC20; JMJD6; PAWR; IMPDH1; TNFRSF19; TMEM155; PTPN14; SLCO2A1; VSIR; CRIM1-DT; SEPTIN11; DZIP1L; SHB; NLRP1; SKA1; PSG1; LDHAP4; TEAD4; DOCK10; SHCBP1; PKP4; PADI2; RAD18; CDC45; AC008543.1; PDGFA; HYI; MTCL1; RRM1; RFC2; AL590004.3; BYSL; RAD51; POLQ; NAT1; POLR3K; VKORC1L1; LIMS2; AC125807.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -706,26 +706,26 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.970873786407767</v>
+        <v>0.888050314465409</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>0.0913924325943768</v>
+        <v>0.0294936424723046</v>
       </c>
       <c r="E8">
-        <v>0.233171606192579</v>
+        <v>-0.247657763213712</v>
       </c>
       <c r="F8">
-        <v>0.902482974989089</v>
+        <v>-0.890140772356946</v>
       </c>
       <c r="G8">
-        <v>842</v>
+        <v>871</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MAN1C1; SLC7A7; FNDC5; SOX9-AS1; MROH7; AP002985.1; LINC02606; ZNF345; RAB3C; KLRG1; AL161729.1; CYB561; AC120049.1; TLR1; KLHL3; PROX1; SLC45A1; ZNF582; PCDHB18P; AK8; CAPN3; YPEL1; INKA2-AS1; VWA5A; GSDMB; TCAP; GAREM1; AC027228.2; AP003498.1; CSPG4P5; AL139384.2; TTC39A; SLC44A3-AS1; TSHZ2; SOX5; LRRC56; AC244197.3; CEP126; ZC3H12B; RAPGEF3; ZCWPW2; PLA2G4C; ASGR1; TCF7; SYNE2; CAB39L; DGKI; AC100786.1; TMEM100; PIK3R3; GAS7; ISLR; ATP6V1FNB; UBA7; CRYBG3; AL356599.1; MTUS2; HMCN1; LDHD; SGMS1-AS1; CMPK2; RABL2A; ESRRG; HGFAC; ABCG1; ZNF578; NIPSNAP3B; NPEPL1; AC093908.1; NUDT7; MRAP2; MINDY1; IL33; LINC01518; SCUBE1; AC139887.2; AC244517.1; ANPEP; ZNF224; LINC02035; TRIL; MANSC1; LINC02249; SYT9; PRCD; AC068580.4; ADAM22; DUSP15; AC102953.2; AP000866.1; TLE3; ITPR1; ZSCAN23; GOLGA6L5P; PI4KAP1; SLC16A9; SLCO2B1; RAB33A; ZNF441; SEMA6A; BTN3A1; PHETA1; PTCH2; PABPC5; MIR600HG; WDR31; LINC02593; ZNF33B; TRANK1; LINC02268; AL137002.2; CACNA1G; C14orf93; AL683813.2; KLHL24; ST3GAL6; ZNF34; AC092691.1; GARNL3; SGPP2; ACCS; UNC79; AC009113.1; SERF1B; HBP1; P2RX7; ZNF233; IL17RC; CHRM2; SHOX2; RAB7B; RNF13; DUSP10; UNC5A; CXXC4; TSPOAP1; WNT11; ZBTB25; HS2ST1; NTNG2; BCL2L11; AFF2; PPEF1; MFSD6; SERPING1; AHCYL2; CDKN1C; TTBK2; WEE2-AS1; NGFR; PLCD4</t>
+          <t>AC023509.1; FP236383.3; ZNF658B; AC068533.4; PCDHB19P; VWF; ADHFE1; AFAP1L2; CHRD; MROH6; C9orf50; AC245407.2; TRIM73; AVPR1B; SLC38A3; SLC34A2; NUDT4P2; ROM1; JAG2; H2BC20P; KCND1; GIPR; ATP8A2; ZNF337-AS1; CACNB2; NYAP1; RAG1; EMID1; RAB11B-AS1; KCNAB2; SLC25A29; DUSP2; DNM1P51; SCN7A; IRF6; ZNF425; ZBTB20; ADGRB1; ADAMTS17; AC074212.1; ZNF606; GOLGA8N; VMAC; COL9A2; NTRK3; FBXL8; PPM1N; ADRA2B; AC026801.2; MYO15B; CCT6B; NRG3; FIGNL2; AZIN2; TMEM169; C2orf27A; CAPS2; AC092275.1; TCAF1P1; CREBRF; HIF3A; LINC00869; AC074143.1; STBD1; ZNF436-AS1; PRRT1; CREB3L4; NHLRC4; TBX19; ANKRD44; RGS14; AC027601.4; AL078621.3; DEPP1; PCDHB3; SCN3A; PLA2G6; NTN3; LINC02604; SILC1; CHST11; DEPTOR; TPBGL; VPS37D; GSEC; ODF3B; ZNF704; GATA3-AS1; AL022069.3; CBLB; ADAMTS10; YPEL4; CASP9; C1QTNF5; PTN; PCDHGA1; ZNF836; CALCOCO1; TVP23C-CDRT4; AL590560.3; AC022007.1; PAXIP1-AS2; LOH12CR2; ZFYVE1; NRG2; PGAP3; APBB3; AC073111.4; DOCK6; TTC28; FAM110B; KLF9; ZNF235; FOXO4; FRAT1; STRA6; KLC4; TMEM130; COL9A3; ZCCHC24; CMTM4; B3GALT4; CAPS; LMTK3; CUL9; FANK1; LRRN3; FOXO6; NINL; ODAM; ZNF821; SNAI1; LDLRAD4; LIN7B; NPTXR; DNMT3A; TMEM116; NOL3; LYRM9; C11orf96; TBX2-AS1; B3GNT9; FAM89B; MARCHF8; C17orf100; SDK2; PPP1R13B; LSAMP; FAHD2B; LINC00174; MAGED4B; BMF; OTULINL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
